--- a/artfynd/A 53862-2022 artfynd.xlsx
+++ b/artfynd/A 53862-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53862-2022 artfynd.xlsx
+++ b/artfynd/A 53862-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105373819</v>
+        <v>93783664</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Virserum, Sm</t>
+          <t>Ekängen, 500 m SO, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533710.0347410839</v>
+        <v>533726</v>
       </c>
       <c r="R2" t="n">
-        <v>6352906.523155544</v>
+        <v>6352957</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-12-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-12-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,33 +758,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Låga i banvallskanten</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Tommy Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Tommy Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105373820</v>
+        <v>105373819</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533693.6268607479</v>
+        <v>533710</v>
       </c>
       <c r="R3" t="n">
-        <v>6352796.224496656</v>
+        <v>6352907</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -860,19 +850,9 @@
           <t>2022-12-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-12-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +876,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>105373820</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Virserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>533693</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6352796</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-12-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-12-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53862-2022 artfynd.xlsx
+++ b/artfynd/A 53862-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93783664</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105373819</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,8 +988,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105373820</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>